--- a/حسابداری/بانک ها/ملت/1405/14050331-14050431.xlsx
+++ b/حسابداری/بانک ها/ملت/1405/14050331-14050431.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\ملت\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE64254-25DD-44B0-8522-3B59655897A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08A8D2A-3F46-499D-87F7-08901A765C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -197,7 +197,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,12 +219,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,7 +251,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -290,12 +284,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1005,7 +993,7 @@
       <c r="E11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="11">
         <v>250000000</v>
       </c>
       <c r="G11" s="3">
@@ -1016,7 +1004,7 @@
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="12">
+      <c r="K11" s="10">
         <v>190</v>
       </c>
       <c r="L11" s="3"/>
@@ -1188,22 +1176,22 @@
     <row r="18" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18"/>
       <c r="B18"/>
-      <c r="C18" s="14"/>
+      <c r="C18" s="12"/>
       <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19"/>
       <c r="B19"/>
-      <c r="C19" s="14"/>
+      <c r="C19" s="12"/>
       <c r="D19"/>
       <c r="E19"/>
       <c r="F19"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
